--- a/data/tech_guidance.xlsx
+++ b/data/tech_guidance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\shenetapp01\Pupil Place Planning\Scorecards\Scorecards 2024\Combined years\technical guidance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmiller3\repos\la-school-places-scorecard-internal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E79E806B-0C3D-4EA2-98AE-858B85EF11E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62591664-EEA0-428C-BFDE-3207C90A1360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5355" windowWidth="38640" windowHeight="21120" xr2:uid="{9CCC1F63-2262-45DD-B4CA-7C937E5C8E7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{9CCC1F63-2262-45DD-B4CA-7C937E5C8E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Quantity" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="245">
   <si>
     <t>Notes</t>
   </si>
@@ -197,9 +197,6 @@
 </t>
   </si>
   <si>
-    <t>5. Total number of planned places (sum of 1, 2, 3, 4 and 5 above)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Number of pupils in roll in January 2010, including dual registrations, in reception to year 11 in the following types of schools: Academy converter, Academy sponsor led, City technology college. Community school, Foundation school, Free schools, Studio schools, University technical college, Voluntary aided school, Voluntary controlled school. </t>
   </si>
   <si>
@@ -207,9 +204,6 @@
   </si>
   <si>
     <t>Total places created between May 2010 and May 2023</t>
-  </si>
-  <si>
-    <t>2.Capacity at May 2023</t>
   </si>
   <si>
     <t>1. The number of places that have been created since May 2010 in each local authority is taken as the difference between capacity as reported by local authorities, via SCAP, at May 2010 and May 2023.
@@ -304,11 +298,6 @@
   </si>
   <si>
     <t>Local authority data provided through the  School Capacity (SCAP) Collection 2023</t>
-  </si>
-  <si>
-    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2025/26 as provided in SCAP 2023.
-2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
-3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.</t>
   </si>
   <si>
     <t>Forecast accuracy of pupil projections for 2023/24</t>
@@ -449,9 +438,6 @@
 </t>
   </si>
   <si>
-    <t>Ranks local authorities on their proportion of new school places of new school places created in well above- and above-average schools</t>
-  </si>
-  <si>
     <t>1. Ranking of proportions of new places created in 'well above average' and 'above average' schools for each local authority, amongst all local authorities with new places. Local authorities with the same proportion are given an equal ranking. Ranking is only applied to local authorities where new places have been created.
 2. The higher the rank the higher the proportion of new school places in well above and above average schools compared to other local authorities.</t>
   </si>
@@ -504,180 +490,6 @@
     <t xml:space="preserve">The national average has been adjusted to the relevant region for each local authority, using the Building Cost Information Service (BCIS) March 2024 published regional location factors. The England national average has been multiplied by the relevant regional location factor:  East Midlands: 1.03, East of England 0.99, Inner London: 1.29, North East: 0.91, North West: 1, Outer London: 1.21, South East: 1.13, South West: 1.01, West Midlands: 0.96, Yorkshire &amp; the Humber: 0.91. </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the 2018, 2019 and 2021 Scorecards. For the 2023 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2024 prices). National averages adjusted for 2023 regional location factors are shown. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(see examples below).
-&lt;br&gt;2. Projects which do not create additional mainstream places or where the project's additional place funding is zero are removed.
-&lt;br&gt;3. Projects were identified as primary  or secondary phase based on additional mainstream place year group breakdown. Where a project created places across both phases, it was assigned a phase corresponding to the phase of the school it affected (i.e. if its school was middle-deemed primary - the project was assigned to primary).
-&lt;br&gt;4. Average cost per place figures for all-through, middle-deemed primary and middle-deemed secondary schools have not been calculated separately due to low sample sizes for these project types. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>To estimate average cost per place for middle-deemed primary schools, we recommend using primary average cost per place</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as the middle school provides education equivalent to the education a primary school provides for all year groups. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>To estimate average cost per place for middle-deemed secondary schools, we recommend using secondary average cost per place</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for the same reason. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>For new middle schools or whole school expansions for middle schools not ‘deemed’ primary or secondary, we recommend taking a mid-point of the primary and secondary costs if the project covers both primary- and secondary-equivalent year groups equally</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (e.g. 2 classes per Year 5 &amp; 6 and 2 classes per Year 7 &amp; 8). </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If the project only covers certain year groups, we recommend using primary cost data if only primary-equivalent years groups are expanding</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (e.g. Years 5 &amp; 6) and </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>secondary data if only secondary-equivalent year groups are expanding</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (e.g. Years 7 &amp; 8).
-&lt;br&gt;5. The average cost does not include costs associated with land acquisition.
-&lt;br&gt;6. The average cost includes costs associated with maintenance and building condition or enhancement works.
-&lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). Where a project creates additional mainstream places and also creates SEN places or re-provides places, an adjustment has been applied to apportion out those costs. 
-&lt;br&gt;8. All costs have been normalised to a common UK average price level using regional location factors published by BCIS, March 2024, 1 is the base weight.
-&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2024.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2024 prices using this index (Q1 2024 index value = 390).
-10. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>To adjust the national average to current or future prices, you need to uprate or downrate the prices in this scorecard relative to the change that has happened since Q1 2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/390).  If not, you can apply a known change to the published cost (e.g. up or down x%).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Example: New primary school in Outer London Q3 (Jul - Sep) 2024.  
-National average for primary new school place = £23,865. 
-Outer London location factor = 1.21 (taken from published BCIS regional location factors March 2023)
-Inflation weight = 394/390 = 1.01 ( taken from BCIS All-In TPI published March 2023). 
-Average primary New School place cost that applies to Outer London in Q3 2023 prices = £23,192 x 1.21 x 1.01 = £29,200 (rounded to nearest £100).  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-If you do not have access the BCIS index, but sources say TPI inflation is set to increase by 4% per annum, then approximate inflation weight = 6% (18 months’ worth of inflation) = 1.06.
-11. Some additional but limited benchmark information for similar capital programme schemes carried out by the DfE is available in the National School Delivery Cost Benchmarking study: https://documents.hants.gov.uk/property-services/NationalSchoolDeliveryBenchmarkingreport.pdf</t>
-    </r>
-  </si>
-  <si>
     <t>Publication</t>
   </si>
   <si>
@@ -687,9 +499,6 @@
     <t>1. The number of places that have been created since May 2010 in each local authority is taken as the difference between capacity as reported by local authorities, via SCAP, at May 2010 and May 2024.
 &lt;br&gt;2. The measure includes all primary and middle deemed primary school capacity in the primary phase, and all secondary, middle deemed secondary and all-through school capacity in the secondary phase.
 &lt;br&gt;3. The measure reports net increase in places only, if phase capacity in a local authority has reduced between May 2010 and May 2024, this is recorded as zero places created. Therefore the sum of the local authority-level figures will not equal the overall increase in places at national level.</t>
-  </si>
-  <si>
-    <t>2.Capacity at May 2024</t>
   </si>
   <si>
     <t>Local authority data provided through School Capacity (SCAP) Survey 2024</t>
@@ -776,11 +585,6 @@
   </si>
   <si>
     <t>Local authority data provided through the  School Capacity (SCAP) Collection 2024</t>
-  </si>
-  <si>
-    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2026/27 as provided in SCAP 2024.
-2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
-3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.</t>
   </si>
   <si>
     <t>Total places created between May 2010 and May 2024</t>
@@ -978,8 +782,277 @@
     <t xml:space="preserve">The national average has been adjusted to the relevant region for each local authority, using the Building Cost Information Service (BCIS) March 2023 published regional location factors. The England national average has been multiplied by the relevant regional location factor:  East Midlands: 1.03, East of England 0.99, Inner London: 1.29, North East: 0.91, North West: 1, Outer London: 1.21, South East: 1.13, South West: 1.01, West Midlands: 0.96, Yorkshire &amp; the Humber: 0.91. </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the 2018, 2019 and 2021 Scorecards. For the 2024 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2025 prices). National averages adjusted for 2024 regional location factors are shown. You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed (see examples below).
+    <t>2024/25</t>
+  </si>
+  <si>
+    <t>Total places created between May 2010 and May 2025</t>
+  </si>
+  <si>
+    <t>Local authority data provided through School Capacity (SCAP) Survey 2025</t>
+  </si>
+  <si>
+    <t>1. The number of places that have been created since May 2010 in each local authority is taken as the difference between capacity as reported by local authorities, via SCAP, at May 2010 and May 2025.
+&lt;br&gt;2. The measure includes all primary and middle deemed primary school capacity in the primary phase, and all secondary, middle deemed secondary and all-through school capacity in the secondary phase.
+&lt;br&gt;3. The measure reports net increase in places only, if phase capacity in a local authority has reduced between May 2010 and May 2025, this is recorded as zero places created. Therefore the sum of the local authority-level figures will not equal the overall increase in places at national level.</t>
+  </si>
+  <si>
+    <t>Number of new places planned for delivery between May 2025 and September 2027;
+&lt;br&gt;This contains: 
+&lt;br&gt;1) local authority firm plans for new permanent additional places , new temporary bulge places and the removal of places,
+&lt;br&gt;2) capacity changes through the Condition Improvement Fund (CIF), School Rebuilding Programme (SRP), Selective Schools Expansion Fund (SSEF), and Voluntary Aided Schools Fund (VA)
+&lt;br&gt;3) places from free schools opened in September 2025 and planned to open in September 2026
+&lt;br&gt;4) reduction in places from free school and academy closures.</t>
+  </si>
+  <si>
+    <t>1. Local authority plans for places to be created or removed between May 2025 and before the start of the 2027/28 academic year.</t>
+  </si>
+  <si>
+    <t>4. Reduction in places from free school and academy closures between May 2025 and January 2026 or identified/confirmed to close before August 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Local authority data about new permanent additional places, new temporary bulge places (to accommodate large cohorts as they move through the school) and permanent places to remove  2025/26, 2026/27  and 2027/28 is aggregated to local authority level.
+&lt;br&gt;2. The data was provided by local authorities in May 2025, and only includes projects they were confident would proceed. Local authorities were asked to include the total places of any new provision, even if spaces would fill gradually. 
+&lt;br&gt;3. Local authorities were asked not to include places created through free schools unless they were providing the funding for additional places themselves. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Changes to school capacity (both increases and decreases) as a consequence of works delivered through the CIF, SRP, SSEF, VA between 2025/26 and 2027/28 inclusive, aggregated to local authority level. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The calculation mirrors the approach taken for basic need funding allocations published in March 2026. It includes mainstream primary and secondary free schools which opened in September 2025 and those with a high degree of certainty of opening in September 2026, and counts the total number of places which will be in use by September 2027.
+&lt;br&gt;2. The data does not include free schools which opened before September 2025, as they will already be included in SCAP25 and are therefore existing places. It does not include free schools which are planned to open in the academic year 2027/28 and beyond. </t>
+  </si>
+  <si>
+    <t>1. Where an academy or free school closed after 1 May 2025 its capacity, as reported in the School Capacity data, is now no longer available. Their capacity has therefore been removed from the planned delivery total.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. This measure reports planned increases in capacity only. If there is a total net planned reduction in capacity (e.g. due to a free school closure), this is shown as zero places planned. Therefore the sum of local authority-level figures will not equal the national planned places figure.
+&lt;br&gt;2. Most local authorities will have further developed their plans since this data was reported in Summer 2025, and so although it allows for comparisons between local authorities, the figure is likely to be an understatement of the current position. </t>
+  </si>
+  <si>
+    <t>Unfilled places in 2024/25</t>
+  </si>
+  <si>
+    <t>Additional places needed in 2027/28; spare places in 2027/28</t>
+  </si>
+  <si>
+    <t>Estimated number of additional places needed to meet demand in 2027/28; estimated percentage of spare places in 2027/28.</t>
+  </si>
+  <si>
+    <t>1.This relates to the academic year 2027/28 and is the difference between local authority pupil forecasts and future capacity, taking account of planned future additions and places to remove.
+     places needed = forecast demand - (existing capacity + additional capacity - places to remove).  
+For further information on the methodology used, see the School Place Planning 2025: technical note found on the School Capacity 25 publication on Explore Education Statistics.
+&lt;br&gt;2. Where demand is greater than capacity a need for additional places results; where capacity is greater than demand spare places result. 
+&lt;br&gt;3. Local authority pupil forecasts for 2027/28 are collected through SCAP 2025&lt;br&gt;4. Additional capacity as at 2027/28 includes places that the local authority plans to add or remove between May 2025 and before the start of the 2027/28 academic year and places from programmes centrally funded by the department, as described above. 
+&lt;br&gt;5. The comparison of demand and capacity takes place for each national curriculum year group within each planning area to estimate places needed in each. The estimates in the scorecard do not allow for spare capacity in one year group or planning area to be off-set against need in another, or vice-versa. This avoids the risk of spare places in one or more planning areas masking areas of need for additional places in planning areas elsewhere in the local authority. For further information see the School Place Planning Tables 2025: technical note.
+&lt;br&gt;6. The estimated need for additional places and estimated spare places is calculated at planning area level and then aggregated to local authority level. It is common for a local authority to have both a need for additional places and spare places, reflecting pockets of localised need for places or pockets of localised spare places.
+&lt;br&gt;7. Estimates for need are rounded to the nearest 10.
+&lt;br&gt;8. Estimates for spare places are presented as a percentage of total future capacity.</t>
+  </si>
+  <si>
+    <t>Change in pupil numbers
+2009/10 to 2025/26; Anticipated change in pupil numbers 2025/26 to 2027/28</t>
+  </si>
+  <si>
+    <t>The actual percentage change in pupil numbers between 2009/10, 2014/15 (for secondary), 2018/19 (for primary) and 2025/26; the anticipated percentage change in pupil numbers in primary or secondary state-funded mainstream provision between the 2025/26 and 2027/28 academic years.</t>
+  </si>
+  <si>
+    <t>4. Pupil Numbers for the 2025/26 academic year taken from the pupil census in January 2026</t>
+  </si>
+  <si>
+    <t>5. Forecast pupil numbers for the 2027/28 academic year</t>
+  </si>
+  <si>
+    <t>Local authority data provided through the  School Capacity (SCAP) Collection 2025</t>
+  </si>
+  <si>
+    <t>School census Jan 2026 data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Number of pupils in roll in January 2026, including dual registrations, in reception to year 11 in the following types of schools: Academy converter, Academy sponsor led, City technology college. Community school, Foundation school, Free schools, Studio schools, University technical college, Voluntary aided school, Voluntary controlled school. 							</t>
+  </si>
+  <si>
+    <t>Local authority data provided through the School Capacity (SCAP) Survey 2025.</t>
+  </si>
+  <si>
+    <t>Forecast accuracy of pupil projections for 2025/26</t>
+  </si>
+  <si>
+    <t>The three year ahead forecast accuracy compares actual pupil numbers on roll with forecasts of pupil numbers for 2025/26 made three years previously (in SCAP 2023) by local authority).</t>
+  </si>
+  <si>
+    <t>1. Forecasts of academic year 2025/26 pupil numbers made in 2024/25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Actual pupil numbers on roll in academic year 2025/26.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Forecasts of academic year 2025/26 pupil numbers made in 2022/23.
+</t>
+  </si>
+  <si>
+    <t>2. Actual pupil numbers on roll in academic year 2025/26.</t>
+  </si>
+  <si>
+    <t>1. Forecasts, submitted by local authorities for SCAP25, at planning area level and aggregated to local authority level. Forecasts include pupils expected to be educated in new schools (or expanded schools) funded through Housing Developer Contributions (HDC) and Housing Infrastructure Fund (HIF) agreements.
+&lt;br&gt;2. Actual pupil numbers on roll for academic year 2025/26 are taken from the January school census and aggregated to local authority level. They include pupils in roll, including dual registrations, in reception to year 11 in the following types of schools: Academy converter, Academy sponsor led, City technology college. Community school, Foundation school, Free schools, Studio schools, University technical college, Voluntary aided school, Voluntary controlled school. &lt;br&gt;3. Forecast accuracy is calculated by  subtracting the years R-6 actual numbers from the years R-6 forecasts to give the absolute inaccuracy. Absolute inaccuracy is then divided by the R-6 actual number to give the relative percentage inaccuracy. The same is done for secondary using years 7-11. 
+&lt;br&gt;4.  Scorecard figures may differ to those published in SCAP due to the exclusion of years 12 to 14 in the pupil numbers and forecasts used in the scorecard.</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Forecasts, submitted by local authorities</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as part of the SCAP 2023, at planning area level and aggregated to local authority level. Forecasts include pupils expected to be educated in new schools (or expanded schools) funded through HDC and HIF agreements.
+&lt;br&gt;2. Actual pupil numbers on roll for academic year 2025/26 are taken from the January school census and aggregated to local authority level. They include pupils in roll, including dual registrations, in reception to year 11 in the following types of schools: Academy converter, Academy sponsor led, City technology college. Community school, Foundation school, Free schools, Studio schools, University technical college, Voluntary aided school, Voluntary controlled school. 	&lt;br&gt;3. Forecast accuracy is calculated by subtracting the years R-6 actual numbers from the years R-6 forecasts to give the absolute inaccuracy. Absolute inaccuracy is then divided by the R-6 actual number to give the relative percentage inaccuracy. The same is done for secondary using years 7-11. 
+&lt;br&gt;4.  Scorecard figures may differ to those published in SCAP due to the exclusion of years 12 to 14 in the pupil numbers and forecasts used in the scorecard.</t>
+    </r>
+  </si>
+  <si>
+    <t>Local authority data provided through the School Capacity (SCAP) Collection 2025</t>
+  </si>
+  <si>
+    <t>Pupils in school provided through the January 2026 School Census</t>
+  </si>
+  <si>
+    <t>School place offers by preference for September 2026 entry</t>
+  </si>
+  <si>
+    <t>The proportion of applicants who received an offer of a place in one of their top three preference schools for September 2026 on national offer day</t>
+  </si>
+  <si>
+    <t>Published School Applications and Offer data 2026/27 Academic Year</t>
+  </si>
+  <si>
+    <t>Quality of new school places created between academic year 2023/24 and 2024/25, based on Ofsted rating</t>
+  </si>
+  <si>
+    <t>The number of new places created between academic year 2023/24 and academic year 2024/25</t>
+  </si>
+  <si>
+    <t>Capacity of each school in May 2024</t>
+  </si>
+  <si>
+    <t>Capacity for each school in May 2025</t>
+  </si>
+  <si>
+    <t>Local authority data, provided through School Capacity collection 2025</t>
+  </si>
+  <si>
+    <t>Quality of school places created between academic year 2023/24 and academic year 2024/25, based on Ofsted rating. The quality of existing school places (places in 2024/25 which were also present in 2023/24) is shown for context.</t>
+  </si>
+  <si>
+    <t>Percentage of new places created in good and outstanding schools between academic year 2024/25 and academic year 2025/26.</t>
+  </si>
+  <si>
+    <t>The quality of school places created between academic year 2023/24 and academic year 2024/25, and the quality of existing school places. Based on key stage 2 progress measures</t>
+  </si>
+  <si>
+    <t>Quality of new school places created between academic year 2023/24 and 2024/25, based on key stage 2 progress measures</t>
+  </si>
+  <si>
+    <t>The quality of school places created between academic year 2023/24 and academic year 2024/25, and the quality of existing school places. Based on key stage 4 progress 8 measure</t>
+  </si>
+  <si>
+    <t>Quality of new school places created between academic year 2023/24 and 2024/25, based on key stage 4 progress 8 measure</t>
+  </si>
+  <si>
+    <t>Percentage of new places created in well above and above-average schools between academic year 2023/24 and academic year 2024/25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Each school has been matched with the key stage 4 progress 8 measure across 8 key subjects, for academic year ending July 2024 (published February 2025). It was not possible to calculate Progress 8 for 2024/25 and 2025/26, because there is no KS2 prior attainment to use to calculate progress when relevant cohorts reach the end of KS4, as primary tests and assessments were cancelled in academic years 2019/20 and 2020/21 due to COVID-19 disruption.
+2. This measure judges schools’ performance as 'well above average', 'above average', 'average', 'below average' or 'well below average'.
+3. The calculation counts the number of new school places that have been created in schools of each category; and the number of existing school places in each category.
+4. Note that middle schools will not have a key stage 4 measure, and that new schools may not have a key stage 4 measure until the first cohort of pupils reaches year 11.
+5. Note that this progress 8 measure is not a strict measure of the effectiveness of the entire school as a school may add value before pupils take the key stage tests. 
+6. For further information on progress 8 measure please use the following url: https://www.gov.uk/government/collections/school-performance-tables-about-the-data 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Each school has been matched with the key stage 2 progress measure for reading and maths, for academic year ending July 2023 (published December 2023). It was not possible to calculate KS1-KS2 progress measures for the 2023/24 and 2024/25 academic years, because there is no relevant KS1 data required to calculate KS1-KS2 progress measures for these cohorts, as primary tests and assessments were cancelled in academic years 2019/20 and 2020/21 due to COVID-19 disruption.
+2. This measure judges schools’ performance as 'well above average', 'above average', 'average', 'below average' or 'well below average'.
+3. The calculation counts the number of new school places that have been created in schools of each category; and the number of existing school places in each category.
+4. Middle schools may not have a key stage 2 measure and if they do, due to the age range of pupils at middle schools, pupils will have only attended a middle school for a short time before they take their key stage 2 tests and will still have a number of years left at the school. This should be taken into account when comparing their results to schools which start educating their pupils from the beginning of key stage 1.  New schools may not have a key stage 2 measure until the first cohort of pupils reaches year 6.
+5. For further information on key stage 2 progress measures please use the following url: https://www.gov.uk/government/collections/school-performance-tables-about-the-data </t>
+  </si>
+  <si>
+    <t>1. The following school types, identified using Get Information About Schools, have been excluded:
+&lt;br&gt;- former independent schools which have not had an inspection since opening;
+&lt;br&gt;- sponsored academies which have not had an Ofsted inspection since opening as an academy.
+&lt;br&gt;- schools that have amalgamated and have not been inspected since amalgamation.
+&lt;br&gt;- schools which have split and have not been inspected since the split.
+&lt;br&gt;2.The capacity of schools present in May 2025 is compared with May 2024 capacity.
+&lt;br&gt;3. New places are identified as an increase in school capacity of 30 places or more between May 2024 and May 2025 at each school. For mergers and academy conversions where 2024 capacity is not available, the capacities of the ‘parent’ schools in 2024 have been used.
+&lt;br&gt;4. Schools where fewer than 30 places have been created between May 2024 and May 2025 have all of their capacity counted as existing places.
+&lt;br&gt;5. Existing places are the number of places present in May 2025 after subtracting the new places since May 2024 (if 30 or more) from the May 2024 capacity.
+&lt;br&gt;6. Primary places are based on primary capacity and secondary places are based on secondary capacity reported in May 2024 or 2025. 
+&lt;br&gt;7. New places in schools which had not had an Ofsted judgment or key stage 2 or 4 result by August 2025 have been excluded from the relevant version of the measure. These places are included in the figure beneath the chart.
+&lt;br&gt;8. Because any decreases in capacity are not factored, the number of places added for use in the quality measure may not be the same as the number of places added in the quantity measure.
+&lt;br&gt;9. From June 2019 the Ofsted grades of academy predecessor schools were factored into their data, even though it may have been some time since those schools converted and/or were inspected. 
+&lt;br&gt;10. The quality measures represent the window in time when places were added and this is not necessarily the same quality outcome as when the decision to add places was taken.</t>
+  </si>
+  <si>
+    <t>The one year ahead local authority forecast accuracy. It compares actual numbers on roll in 2025/26 with forecasts of pupil numbers for 2025/26 made one year previously (in SCAP 2025)</t>
+  </si>
+  <si>
+    <t>3. Places from free schools opened in September 2025 and due to be opened in September 2026.</t>
+  </si>
+  <si>
+    <t>5. Total number of planned places (sum of 1, 2, 3 and 4 above)</t>
+  </si>
+  <si>
+    <t>Ranks local authorities on their proportion of new school places created in well above- and above-average schools</t>
+  </si>
+  <si>
+    <t>2. Capacity at May 2023</t>
+  </si>
+  <si>
+    <t>2. Capacity at May 2024</t>
+  </si>
+  <si>
+    <t>2. Capacity at May 2025</t>
+  </si>
+  <si>
+    <t>Places planned to 2027/28</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the 2018, 2019 and 2021 Scorecards. For the 2023 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2024 prices). National averages adjusted for 2023 regional location factors are shown. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(see examples below).
 &lt;br&gt;2. Projects which do not create additional mainstream places or where the project's additional place funding is zero are removed.
 &lt;br&gt;3. Projects were identified as primary  or secondary phase based on additional mainstream place year group breakdown. Where a project created places across both phases, it was assigned a phase corresponding to the phase of the school it affected (i.e. if its school was middle-deemed primary - the project was assigned to primary).
 &lt;br&gt;4. Average cost per place figures for all-through, middle-deemed primary and middle-deemed secondary schools have not been calculated separately due to low sample sizes for these project types. </t>
@@ -1080,9 +1153,9 @@
       <t xml:space="preserve"> (e.g. Years 7 &amp; 8).
 &lt;br&gt;5. The average cost does not include costs associated with land acquisition.
 &lt;br&gt;6. The average cost includes costs associated with maintenance and building condition or enhancement works.
-&lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). For projects within the 2018 Capital Spend dataset, a project which creates additional mainstream places and also creates SEN places or re-provides places, has been adjusted to apportion out those costs. For projects within the Capital Spend Survey, apportioning costs is not possible and therefore a project which creates additional mainstream places and also creates SEN places or re-provides places has been exlcuded.
+&lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). Where a project creates additional mainstream places and also creates SEN places or re-provides places, an adjustment has been applied to apportion out those costs. 
 &lt;br&gt;8. All costs have been normalised to a common UK average price level using regional location factors published by BCIS, March 2023, 1 is the base weight.
-&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2025.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2025 prices using this index (Q1 2025 index value = 399).
+&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2024.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2024 prices using this index (Q1 2024 index value = 390).
 10. </t>
     </r>
     <r>
@@ -1093,16 +1166,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>To adjust the national average to current or future prices, you need to uprate or downrate the prices in this scorecard relative to the change that has happened since Q1 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/399).  If not, you can apply a known change to the published cost (e.g. up or down x%).
+      <t>To adjust the national average to current or future prices, you need to uprate or downrate the prices in this scorecard relative to the change that has happened since Q1 2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/390).  If not, you can apply a known change to the published cost (e.g. up or down x%).
 </t>
     </r>
     <r>
@@ -1131,6 +1204,323 @@
 If you do not have access the BCIS index, but sources say TPI inflation is set to increase by 4% per annum, then approximate inflation weight = 6% (18 months’ worth of inflation) = 1.06.
 11. Some additional but limited benchmark information for similar capital programme schemes carried out by the DfE is available in the National School Delivery Cost Benchmarking study: https://documents.hants.gov.uk/property-services/NationalSchoolDeliveryBenchmarkingreport.pdf</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the 2018, 2019 and 2021 Scorecards. For the 2024 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2025 prices). National averages adjusted for 2023 regional location factors are shown. You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed (see examples below).
+&lt;br&gt;2. Projects which do not create additional mainstream places or where the project's additional place funding is zero are removed.
+&lt;br&gt;3. Projects were identified as primary  or secondary phase based on additional mainstream place year group breakdown. Where a project created places across both phases, it was assigned a phase corresponding to the phase of the school it affected (i.e. if its school was middle-deemed primary - the project was assigned to primary).
+&lt;br&gt;4. Average cost per place figures for all-through, middle-deemed primary and middle-deemed secondary schools have not been calculated separately due to low sample sizes for these project types. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To estimate average cost per place for middle-deemed primary schools, we recommend using primary average cost per place</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the middle school provides education equivalent to the education a primary school provides for all year groups. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To estimate average cost per place for middle-deemed secondary schools, we recommend using secondary average cost per place</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for the same reason. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>For new middle schools or whole school expansions for middle schools not ‘deemed’ primary or secondary, we recommend taking a mid-point of the primary and secondary costs if the project covers both primary- and secondary-equivalent year groups equally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. 2 classes per Year 5 &amp; 6 and 2 classes per Year 7 &amp; 8). </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If the project only covers certain year groups, we recommend using primary cost data if only primary-equivalent years groups are expanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. Years 5 &amp; 6) and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>secondary data if only secondary-equivalent year groups are expanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. Years 7 &amp; 8).
+&lt;br&gt;5. The average cost does not include costs associated with land acquisition.
+&lt;br&gt;6. The average cost includes costs associated with maintenance and building condition or enhancement works.
+&lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). For projects within the 2018 Capital Spend dataset, a project which creates additional mainstream places and also creates SEN places or re-provides places, has been adjusted to apportion out those costs. For projects within the Capital Spend Survey, apportioning costs is not possible and therefore a project which creates additional mainstream places and also creates SEN places or re-provides places has been excluded.
+&lt;br&gt;8. All costs have been normalised to a common UK average price level using regional location factors published by BCIS, March 2023, 1 is the base weight.
+&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2025.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2025 prices using this index (Q1 2025 index value = 399).
+10. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To adjust the national average to current or future prices, you need to uprate or downrate the prices in this scorecard relative to the change that has happened since Q1 2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/399).  If not, you can apply a known change to the published cost (e.g. up or down x%).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Example: New primary school in Outer London Q3 (Jul - Sep) 2024.  
+National average for primary new school place = £23,865. 
+Outer London location factor = 1.21 (taken from published BCIS regional location factors March 2023)
+Inflation weight = 394/390 = 1.01 ( taken from BCIS All-In TPI published March 2023). 
+Average primary New School place cost that applies to Outer London in Q3 2023 prices = £23,192 x 1.21 x 1.01 = £29,200 (rounded to nearest £100).  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+If you do not have access the BCIS index, but sources say TPI inflation is set to increase by 4% per annum, then approximate inflation weight = 6% (18 months’ worth of inflation) = 1.06.
+11. Some additional but limited benchmark information for similar capital programme schemes carried out by the DfE is available in the National School Delivery Cost Benchmarking study: https://documents.hants.gov.uk/property-services/NationalSchoolDeliveryBenchmarkingreport.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the scorecards since 2018. For the 2025 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2026 prices). National averages adjusted for 2023 regional location factors are shown. You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed (see examples below).
+&lt;br&gt;2. Projects which do not create additional mainstream places or where the project's additional place funding is zero are removed.
+&lt;br&gt;3. Projects were identified as primary  or secondary phase based on additional mainstream place year group breakdown. Where a project created places across both phases, it was assigned a phase corresponding to the phase of the school it affected (i.e. if its school was middle-deemed primary - the project was assigned to primary).
+&lt;br&gt;4. Average cost per place figures for all-through, middle-deemed primary and middle-deemed secondary schools have not been calculated separately due to low sample sizes for these project types. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To estimate average cost per place for middle-deemed primary schools, we recommend using primary average cost per place</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the middle school provides education equivalent to the education a primary school provides for all year groups. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To estimate average cost per place for middle-deemed secondary schools, we recommend using secondary average cost per place</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for the same reason. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>For new middle schools or whole school expansions for middle schools not ‘deemed’ primary or secondary, we recommend taking a mid-point of the primary and secondary costs if the project covers both primary- and secondary-equivalent year groups equally</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. 2 classes per Year 5 &amp; 6 and 2 classes per Year 7 &amp; 8). </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If the project only covers certain year groups, we recommend using primary cost data if only primary-equivalent years groups are expanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. Years 5 &amp; 6) and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>secondary data if only secondary-equivalent year groups are expanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. Years 7 &amp; 8).
+&lt;br&gt;5. The average cost does not include costs associated with land acquisition.
+&lt;br&gt;6. The average cost includes costs associated with maintenance and building condition or enhancement works.
+&lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). For projects within the 2018 Capital Spend dataset, a project which creates additional mainstream places and also creates SEN places or re-provides places, has been adjusted to apportion out those costs. For projects within the Capital Spend Survey, apportioning costs is not possible and therefore a project which creates additional mainstream places and also creates SEN places or re-provides places has been excluded.
+&lt;br&gt;8. All costs have been normalised to a common UK average price level using regional location factors published by BCIS, March 2023, 1 is the base weight.
+&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2026.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2026 prices using this index (Q1 2026 index value = 399).
+10. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To adjust the national average to current or future prices, you need to uprate or downrate the prices in this scorecard relative to the change that has happened since Q1 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/399).  If not, you can apply a known change to the published cost (e.g. up or down x%).
+11. Some additional but limited benchmark information for similar capital programme schemes carried out by the DfE is available in the National School Delivery Cost Benchmarking study: https://documents.hants.gov.uk/property-services/NationalSchoolDeliveryBenchmarkingreport.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Each school has been matched with the Ofsted data as at  31 August 2025 (published November 2025). Graded judgements on four areas 'Quality of Education', 'Behaviour and Attitudes', 'Personal Development' and 'Leadership and Management' are used and where the inspection took place before 1 September 2023 the rating for 'Overall effectiveness: how good is the school is." is used for each judgement area.
+&lt;br&gt;2. There are four Ofsted categories: 'Outstanding', 'Good', 'Requires improvement' and 'Inadequate'.
+&lt;br&gt;3. The calculation counts the number of existing and new places that have been created in schools of each category. &lt;br&gt;4. Note that many schools will have been inspected some time before August 2025, and some will have been inspected since this date. &lt;br&gt;5. There are school places with no rating, as the school has yet to be inspected so do not have an Ofsted judgement.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2027/28 as provided in SCAP 2025.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2026/27 as provided in SCAP 2024.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2025/26 as provided in SCAP 2023.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>Total basic need funding 2011 to 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total amount of basic need capital funding allocated to each local authority to support them to create new mainstream primary and secondary places from 2011 to 2028. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. This refers to the amount of basic need capital funding that the Department for Education (DfE) has allocated to each local authority to create new places from the 2011-12 financial year to the 2027-28 financial year. Basic Need funding for the 2027-28 financial year is intended to support the creation of mainstream places for pupils aged 5 to 16 for the 2028/29 academic year. &lt;br&gt;2. The figure includes formula-based funding allocations and funding provided through the Targeted Basic Need Programme. Basic Need formula-based funding allocations cover the whole period and are not ring-fenced (although they can only be used for capital purposes).  Targeted Basic Need funding was provided between 2013 and 2015 and had to be spent by agreed deadlines and on specific projects. Both types of allocations are published here. &lt;br&gt;3. The figure only includes funding allocated to local authorities and does not include centrally-funded capital programmes such as the free schools programme. &lt;br&gt;4. The England total will not match the sum of allocations for all local authorities in the scorecard because the England total includes allocations to predecessor local authorities.
+</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1598,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,8 +1611,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1472,26 +1868,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1606,47 +2005,69 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1964,17 +2385,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8372DA64-5E2C-41C1-8CF4-85BC1C2AFF86}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="87.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+    <col min="5" max="5" width="87.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1990,492 +2411,753 @@
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="54"/>
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="6"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="7"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="54"/>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="E17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="6"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="56"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="56"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="56"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="57"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="F29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B30" s="61" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D30" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="45"/>
-      <c r="F3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="6" t="s">
+      <c r="E30" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="139.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="54"/>
+      <c r="F31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="6"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E33" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="6"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="6"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="13" t="s">
+      <c r="E35" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="6"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="375" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="45"/>
-      <c r="F16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="13" t="s">
+      <c r="F40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="56"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="13" t="s">
+      <c r="D41" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="13" t="s">
+      <c r="E41" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="13" t="s">
+      <c r="F41" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="56"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="375" x14ac:dyDescent="0.25">
-      <c r="A23" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="20" t="s">
+      <c r="D42" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10" t="s">
+      <c r="E42" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="54"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="F26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="54"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="54"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="F29" t="s">
-        <v>147</v>
+      <c r="F42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A43" s="56"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="57"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F44" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="13">
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:B44"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="B25:B29"/>
@@ -2487,192 +3169,279 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="Local authority data provided through the School Capacity (SCAP) Survey 2022." xr:uid="{77149A54-01F0-45EA-8D19-CDE8AECFE598}"/>
-    <hyperlink ref="D10" r:id="rId2" display=" 2021/22 school place planning published underlying data. " xr:uid="{093B09C6-85AC-4B03-8BE4-078C82660B4C}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{77149A54-01F0-45EA-8D19-CDE8AECFE598}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{093B09C6-85AC-4B03-8BE4-078C82660B4C}"/>
     <hyperlink ref="D2" r:id="rId3" xr:uid="{8150C38D-D188-4C8E-86C3-B5575B8FFEE8}"/>
     <hyperlink ref="D11" r:id="rId4" xr:uid="{84C17436-4B87-48EB-BAE5-31DBACCBDB31}"/>
-    <hyperlink ref="D13" r:id="rId5" display="School census Jan 2023 data" xr:uid="{B4335ED1-45C2-43A8-BAE4-D6C4C7E179D0}"/>
+    <hyperlink ref="D13" r:id="rId5" xr:uid="{B4335ED1-45C2-43A8-BAE4-D6C4C7E179D0}"/>
     <hyperlink ref="D12" r:id="rId6" xr:uid="{CCB6838D-DD36-44DD-BC08-5E652C942FA3}"/>
-    <hyperlink ref="D9" r:id="rId7" display="Local authority data provided through School Capacity (SCAP) Survey 2021" xr:uid="{F7517439-C801-46CD-8DC3-B6DD58F4289A}"/>
-    <hyperlink ref="D14" r:id="rId8" display="Local authority data provided through the  School Capacity (SCAP) Collection 2022" xr:uid="{2257ADC3-56E0-46AA-984A-65A14B6B91D4}"/>
-    <hyperlink ref="D17" r:id="rId9" display="Local authority data provided through the School Capacity (SCAP) Survey 2022." xr:uid="{D140B5FC-6CE2-48F1-BF21-C9EC2586782D}"/>
-    <hyperlink ref="D23" r:id="rId10" display=" 2021/22 school place planning published underlying data. " xr:uid="{168FA84B-11B4-4C80-A7A5-597B690A65BF}"/>
+    <hyperlink ref="D9" r:id="rId7" xr:uid="{F7517439-C801-46CD-8DC3-B6DD58F4289A}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{2257ADC3-56E0-46AA-984A-65A14B6B91D4}"/>
+    <hyperlink ref="D17" r:id="rId9" xr:uid="{D140B5FC-6CE2-48F1-BF21-C9EC2586782D}"/>
+    <hyperlink ref="D23" r:id="rId10" xr:uid="{168FA84B-11B4-4C80-A7A5-597B690A65BF}"/>
     <hyperlink ref="D15" r:id="rId11" xr:uid="{D7EB4574-CB25-42A9-B4C2-3913F62B5513}"/>
     <hyperlink ref="D24" r:id="rId12" xr:uid="{3D41CC56-05BA-471B-ABB1-3CB74AC2778A}"/>
-    <hyperlink ref="D28" r:id="rId13" display="School census Jan 2023 data" xr:uid="{F0889FF8-A60B-411C-A004-D5DA89758A71}"/>
+    <hyperlink ref="D28" r:id="rId13" xr:uid="{F0889FF8-A60B-411C-A004-D5DA89758A71}"/>
     <hyperlink ref="D25" r:id="rId14" xr:uid="{57A1343E-B39E-429E-94B0-FD3C6471C21E}"/>
-    <hyperlink ref="D22" r:id="rId15" display="Local authority data provided through School Capacity (SCAP) Survey 2021" xr:uid="{4E4AE6EF-3D53-4105-97A1-065AADC66650}"/>
-    <hyperlink ref="D29" r:id="rId16" display="Local authority data provided through the  School Capacity (SCAP) Collection 2022" xr:uid="{712DF8AA-676E-41AB-BBBE-2AB832B676D0}"/>
+    <hyperlink ref="D22" r:id="rId15" xr:uid="{4E4AE6EF-3D53-4105-97A1-065AADC66650}"/>
+    <hyperlink ref="D29" r:id="rId16" xr:uid="{712DF8AA-676E-41AB-BBBE-2AB832B676D0}"/>
     <hyperlink ref="D26" r:id="rId17" xr:uid="{506A2691-ED47-412F-A8C0-7648AE09BFD7}"/>
     <hyperlink ref="D27" r:id="rId18" xr:uid="{CC0BA90D-BAE6-4C2F-9262-0D1CAD7283ED}"/>
+    <hyperlink ref="D32" r:id="rId19" xr:uid="{2620CD74-655F-4E47-B27F-FEEE3E0FED48}"/>
+    <hyperlink ref="D38" r:id="rId20" display=" 2021/22 school place planning published underlying data. " xr:uid="{29F5B286-6A53-4701-BFE3-30AB96582F0A}"/>
+    <hyperlink ref="D30" r:id="rId21" xr:uid="{0EDA09B0-4F8F-4DC1-8301-8E8233285AED}"/>
+    <hyperlink ref="D39" r:id="rId22" xr:uid="{7FB8B719-FF5E-4097-B4FE-95E67FF58E30}"/>
+    <hyperlink ref="D43" r:id="rId23" xr:uid="{8D8BD834-06DD-4319-8655-9F1A9BC8B41F}"/>
+    <hyperlink ref="D40" r:id="rId24" xr:uid="{AADA33D8-2C35-499D-8DE7-47C7DFDA9BD0}"/>
+    <hyperlink ref="D37" r:id="rId25" display="Local authority data provided through School Capacity (SCAP) Survey 2021" xr:uid="{6137A55C-4EB2-4C4A-91CC-56A342724F6B}"/>
+    <hyperlink ref="D44" r:id="rId26" xr:uid="{EC15E42B-CC31-4CEB-8D36-F4AD21F7D825}"/>
+    <hyperlink ref="D41" r:id="rId27" xr:uid="{17A39E15-3BDC-4A72-AC38-C75F16C23793}"/>
+    <hyperlink ref="D42" r:id="rId28" xr:uid="{C42D3BF9-4F33-401D-9DAB-DEF4366DB9B5}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{D65EA06E-2FCA-4967-8981-89C1BC679462}"/>
+    <hyperlink ref="D3" r:id="rId30" xr:uid="{A1709877-B282-4D91-8FFE-B46928B2EFAE}"/>
+    <hyperlink ref="D16" r:id="rId31" xr:uid="{E4C2A8F6-C44D-4E43-8648-85C3409F2F1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C67D23D-5B13-4F00-9F83-043839CEFFD1}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="55.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="55.42578125" style="34"/>
+    <col min="1" max="16384" width="55.453125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="F1" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="30"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="D3" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="64"/>
+      <c r="F3" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="30"/>
+      <c r="B4" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="37"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="63"/>
+      <c r="F5" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="30"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="64"/>
+      <c r="F7" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="30"/>
+      <c r="B8" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="37"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="30"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="64"/>
+      <c r="F11" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="30"/>
+      <c r="B12" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="34" t="s">
-        <v>147</v>
+      <c r="E12" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="37"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="63"/>
+      <c r="F13" s="32" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="B4:B5"/>
@@ -2684,26 +3453,34 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="Local authority data provided through the School Capacity (SCAP) Collection 2022" xr:uid="{D14A8E59-0240-4725-B7AC-4582058C6B59}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{D14A8E59-0240-4725-B7AC-4582058C6B59}"/>
     <hyperlink ref="D4" r:id="rId2" xr:uid="{586F3224-6D8F-4AF9-899D-550CFDC0058F}"/>
-    <hyperlink ref="D3" r:id="rId3" display="Pupils in school provided through the January 2023 School Census" xr:uid="{17405BAA-EC5B-41A8-9F2F-BBE920A0B9BB}"/>
-    <hyperlink ref="D5" r:id="rId4" display="Pupils in school provided through the January 2023 School Census" xr:uid="{54B0E578-7E98-4CE5-8BEB-25623CA0296D}"/>
-    <hyperlink ref="D6" r:id="rId5" display="Local authority data provided through the School Capacity (SCAP) Collection 2022" xr:uid="{F94E27B9-93F2-492F-B022-03D1BF2ED50B}"/>
-    <hyperlink ref="D8" r:id="rId6" display="Local authority data provided through the School Capacity (SCAP) Collection 2021" xr:uid="{DB6C9518-4974-4D88-A3FD-A0D73E1156DA}"/>
-    <hyperlink ref="D7" r:id="rId7" display="Pupils in school provided through the January 2023 School Census" xr:uid="{D4EB79EF-B53B-4F30-A202-85F4FBDCA5DB}"/>
-    <hyperlink ref="D9" r:id="rId8" display="Pupils in school provided through the January 2023 School Census" xr:uid="{A8F94BE9-CA43-4F91-A3C7-D2BD25322736}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{17405BAA-EC5B-41A8-9F2F-BBE920A0B9BB}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{54B0E578-7E98-4CE5-8BEB-25623CA0296D}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{F94E27B9-93F2-492F-B022-03D1BF2ED50B}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{DB6C9518-4974-4D88-A3FD-A0D73E1156DA}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{D4EB79EF-B53B-4F30-A202-85F4FBDCA5DB}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{A8F94BE9-CA43-4F91-A3C7-D2BD25322736}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{99C36A94-5EE0-4229-BF2A-697131F0865F}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{2251E3CE-EC88-4AC9-9548-A7852D41C8BA}"/>
+    <hyperlink ref="D11" r:id="rId11" xr:uid="{E8142A28-5803-4E1B-ADBC-4CE1611F4845}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{BFF4449C-F1C9-4F83-AEDB-3EF729ACDA6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3163888B-9214-4218-82C5-5CD72F2D39D0}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="48.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="48.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2719,457 +3496,645 @@
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="F1" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="F2" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="F3" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="58" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="F4" s="43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="58" t="s">
-        <v>147</v>
+      <c r="F5" s="43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="Published School Applications and Offer data 2022/23 Academic Year" xr:uid="{65C563AA-E96A-4DA3-9BD3-0A919A6BB712}"/>
-    <hyperlink ref="D3" r:id="rId2" display="Published School Applications and Offer data 2022/23 Academic Year" xr:uid="{73E1A89E-78ED-4859-B41E-1AE6B97802E3}"/>
-    <hyperlink ref="D4" r:id="rId3" display="Published School Applications and Offer data 2022/23 Academic Year" xr:uid="{DEAC6B57-4AAA-46A4-8F99-7C21A4EAB388}"/>
-    <hyperlink ref="D5" r:id="rId4" display="Published School Applications and Offer data 2022/23 Academic Year" xr:uid="{1A8CD594-5A7A-4EBE-87C4-EDF4055AC3CF}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{65C563AA-E96A-4DA3-9BD3-0A919A6BB712}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{73E1A89E-78ED-4859-B41E-1AE6B97802E3}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{DEAC6B57-4AAA-46A4-8F99-7C21A4EAB388}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{1A8CD594-5A7A-4EBE-87C4-EDF4055AC3CF}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{2A3390A4-90B5-4D49-8B7F-59A281139279}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{9C53285F-4078-415B-8270-E268A35E654C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172A91E8-EE08-4774-802F-E9F4C78EAB63}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="37.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="37.28515625" style="34"/>
-    <col min="5" max="5" width="77.28515625" style="34" customWidth="1"/>
-    <col min="6" max="16384" width="37.28515625" style="34"/>
+    <col min="1" max="4" width="37.26953125" style="32"/>
+    <col min="5" max="5" width="77.26953125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="37.26953125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="F1" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="F2" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D3" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="E3" s="40"/>
+      <c r="F3" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="39"/>
+      <c r="B4" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="13" t="s">
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="203" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="C7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="150" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="43" t="s">
+      <c r="E7" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="13" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="40"/>
+      <c r="F14" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="39"/>
+      <c r="B15" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D15" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="E15" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B16" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="261" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D17" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+      <c r="A23" s="39"/>
+      <c r="B23" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="D24" s="11"/>
+      <c r="E24" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="255" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="F24" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="261" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="240" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="D26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="F27" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="41"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="42"/>
-      <c r="F14" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="150" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="315" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="240" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="F28" s="32" t="s">
         <v>175</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3180,136 +4145,160 @@
     <hyperlink ref="D4" r:id="rId3" xr:uid="{2FB89BF4-390E-4CD5-92FB-FD0FF31F028D}"/>
     <hyperlink ref="D7" r:id="rId4" xr:uid="{4534F643-19C4-4655-8095-8044AC4B7902}"/>
     <hyperlink ref="D8" r:id="rId5" xr:uid="{4889CA3C-1157-412C-ACB1-EE5DA00A90DF}"/>
-    <hyperlink ref="D13" r:id="rId6" display="Local authority data, provided through School Capacity collection 2022" xr:uid="{73725C21-EC8E-495A-8521-6604BDCA9BF5}"/>
-    <hyperlink ref="D14" r:id="rId7" display="Local authority data, provided through School Capacity collection 2023" xr:uid="{3107590D-6B8F-4322-8365-F40271488FAC}"/>
-    <hyperlink ref="D15" r:id="rId8" xr:uid="{169006D7-2497-4BE8-90DB-4A1783604C5F}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{6D9BDEC1-A85B-4BAE-B25C-DC97AE840965}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{D90B4F41-BA2F-44BC-AA85-E0C3BEF1F585}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{73725C21-EC8E-495A-8521-6604BDCA9BF5}"/>
+    <hyperlink ref="D14" r:id="rId7" xr:uid="{3107590D-6B8F-4322-8365-F40271488FAC}"/>
+    <hyperlink ref="D17" r:id="rId8" xr:uid="{6D9BDEC1-A85B-4BAE-B25C-DC97AE840965}"/>
+    <hyperlink ref="D18" r:id="rId9" xr:uid="{D90B4F41-BA2F-44BC-AA85-E0C3BEF1F585}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{46ACBF62-ACD3-4F81-99D8-6C1D0CC2153A}"/>
+    <hyperlink ref="D22" r:id="rId11" xr:uid="{4BBB4DDC-6817-413D-B572-3CD2D1440AC8}"/>
+    <hyperlink ref="D23" r:id="rId12" xr:uid="{3E0C30B7-C9B9-4F71-80E6-83879AE805A9}"/>
+    <hyperlink ref="D25" r:id="rId13" xr:uid="{ECEC2841-C9C1-4A0D-9005-A2B7FE9C1FF8}"/>
+    <hyperlink ref="D26" r:id="rId14" xr:uid="{2DE614D0-6016-4F34-8709-BB2A3D024DC6}"/>
+    <hyperlink ref="D15" r:id="rId15" xr:uid="{169006D7-2497-4BE8-90DB-4A1783604C5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB73E146-A141-4797-B302-F0B3455C0C2E}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="57.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="57.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="57.5703125" style="34"/>
+    <col min="1" max="16384" width="57.54296875" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="F1" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="E2" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C3" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="19"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
+      <c r="E3" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="ec07c698-60f5-424f-b9af-f4c59398b511" ContentTypeId="0x010100545E941595ED5448BA61900FDDAFF313" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Official Document" ma:contentTypeID="0x010100545E941595ED5448BA61900FDDAFF31300C0D9F77D091A79449828113EF8250EF5" ma:contentTypeVersion="9" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="3acf8af8f3f036fb6d934619e757bc96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8c566321-f672-4e06-a901-b5e72b4c4357" xmlns:ns3="2a6436df-3f7a-48ac-8ea6-44b411e24bbc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="926947be84ee9a0228ce6a037c6848ba" ns2:_="" ns3:_="">
     <xsd:import namespace="8c566321-f672-4e06-a901-b5e72b4c4357"/>
@@ -3515,61 +4504,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Value>5</Value>
-      <Value>25</Value>
-      <Value>1</Value>
-      <Value>4</Value>
-    </TaxCatchAll>
-    <p6919dbb65844893b164c5f63a6f0eeb xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a484111e-5b24-4ad9-9778-c536c8c88985</TermId>
-        </TermInfo>
-      </Terms>
-    </p6919dbb65844893b164c5f63a6f0eeb>
-    <c02f73938b5741d4934b358b31a1b80f xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0884c477-2e62-47ea-b19c-5af6e91124c5</TermId>
-        </TermInfo>
-      </Terms>
-    </c02f73938b5741d4934b358b31a1b80f>
-    <f6ec388a6d534bab86a259abd1bfa088 xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">cc08a6d4-dfde-4d0f-bd85-069ebcef80d5</TermId>
-        </TermInfo>
-      </Terms>
-    </f6ec388a6d534bab86a259abd1bfa088>
-    <i98b064926ea4fbe8f5b88c394ff652b xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </i98b064926ea4fbe8f5b88c394ff652b>
-    <_dlc_DocIdUrl xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">
-      <Url>https://educationgovuk.sharepoint.com/sites/efappp/_layouts/15/DocIdRedir.aspx?ID=FKMV6N5X2MYP-1953928680-76369</Url>
-      <Description>FKMV6N5X2MYP-1953928680-76369</Description>
-    </_dlc_DocIdUrl>
-    <_dlc_DocId xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">FKMV6N5X2MYP-1953928680-76369</_dlc_DocId>
-  </documentManagement>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="ec07c698-60f5-424f-b9af-f4c59398b511" ContentTypeId="0x010100545E941595ED5448BA61900FDDAFF313" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -3619,15 +4559,61 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00F0DC4-2D9F-43FC-8616-EC131ED26B7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Value>5</Value>
+      <Value>25</Value>
+      <Value>1</Value>
+      <Value>4</Value>
+    </TaxCatchAll>
+    <p6919dbb65844893b164c5f63a6f0eeb xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a484111e-5b24-4ad9-9778-c536c8c88985</TermId>
+        </TermInfo>
+      </Terms>
+    </p6919dbb65844893b164c5f63a6f0eeb>
+    <c02f73938b5741d4934b358b31a1b80f xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0884c477-2e62-47ea-b19c-5af6e91124c5</TermId>
+        </TermInfo>
+      </Terms>
+    </c02f73938b5741d4934b358b31a1b80f>
+    <f6ec388a6d534bab86a259abd1bfa088 xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">cc08a6d4-dfde-4d0f-bd85-069ebcef80d5</TermId>
+        </TermInfo>
+      </Terms>
+    </f6ec388a6d534bab86a259abd1bfa088>
+    <i98b064926ea4fbe8f5b88c394ff652b xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </i98b064926ea4fbe8f5b88c394ff652b>
+    <_dlc_DocIdUrl xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">
+      <Url>https://educationgovuk.sharepoint.com/sites/efappp/_layouts/15/DocIdRedir.aspx?ID=FKMV6N5X2MYP-1953928680-76369</Url>
+      <Description>FKMV6N5X2MYP-1953928680-76369</Description>
+    </_dlc_DocIdUrl>
+    <_dlc_DocId xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">FKMV6N5X2MYP-1953928680-76369</_dlc_DocId>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E94FF3-D2F7-4169-BE5C-5ED202BAA024}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3646,7 +4632,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00F0DC4-2D9F-43FC-8616-EC131ED26B7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C56A4F-6917-41AA-BBE5-DA7C75896563}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035EEA42-582A-4724-B162-C22729062C2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{334E8BC2-6B82-4EDA-BE50-EFE4767E8CD2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="8c566321-f672-4e06-a901-b5e72b4c4357"/>
@@ -3663,18 +4673,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035EEA42-582A-4724-B162-C22729062C2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C56A4F-6917-41AA-BBE5-DA7C75896563}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{de278828-447b-4aaa-a336-d38da9839a3c}" enabled="1" method="Privileged" siteId="{fad277c9-c60a-4da1-b5f3-b3b8b34a82f9}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/tech_guidance.xlsx
+++ b/data/tech_guidance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmiller3\repos\la-school-places-scorecard-internal\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbrett\repos\la-school-places-scorecards\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62591664-EEA0-428C-BFDE-3207C90A1360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CB439D-05BA-4DB1-B6A5-55831A0081A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{9CCC1F63-2262-45DD-B4CA-7C937E5C8E7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{9CCC1F63-2262-45DD-B4CA-7C937E5C8E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Quantity" sheetId="2" r:id="rId1"/>
@@ -1361,6 +1361,39 @@
     </r>
   </si>
   <si>
+    <t>1. Each school has been matched with the Ofsted data as at  31 August 2025 (published November 2025). Graded judgements on four areas 'Quality of Education', 'Behaviour and Attitudes', 'Personal Development' and 'Leadership and Management' are used and where the inspection took place before 1 September 2023 the rating for 'Overall effectiveness: how good is the school is." is used for each judgement area.
+&lt;br&gt;2. There are four Ofsted categories: 'Outstanding', 'Good', 'Requires improvement' and 'Inadequate'.
+&lt;br&gt;3. The calculation counts the number of existing and new places that have been created in schools of each category. &lt;br&gt;4. Note that many schools will have been inspected some time before August 2025, and some will have been inspected since this date. &lt;br&gt;5. There are school places with no rating, as the school has yet to be inspected so do not have an Ofsted judgement.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2027/28 as provided in SCAP 2025.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2026/27 as provided in SCAP 2024.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2025/26 as provided in SCAP 2023.
+&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
+&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
+&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
+  </si>
+  <si>
+    <t>Total basic need funding 2011 to 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total amount of basic need capital funding allocated to each local authority to support them to create new mainstream primary and secondary places from 2011 to 2028. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. This refers to the amount of basic need capital funding that the Department for Education (DfE) has allocated to each local authority to create new places from the 2011-12 financial year to the 2027-28 financial year. Basic Need funding for the 2027-28 financial year is intended to support the creation of mainstream places for pupils aged 5 to 16 for the 2028/29 academic year. &lt;br&gt;2. The figure includes formula-based funding allocations and funding provided through the Targeted Basic Need Programme. Basic Need formula-based funding allocations cover the whole period and are not ring-fenced (although they can only be used for capital purposes).  Targeted Basic Need funding was provided between 2013 and 2015 and had to be spent by agreed deadlines and on specific projects. Both types of allocations are published here. &lt;br&gt;3. The figure only includes funding allocated to local authorities and does not include centrally-funded capital programmes such as the free schools programme. &lt;br&gt;4. The England total will not match the sum of allocations for all local authorities in the scorecard because the England total includes allocations to predecessor local authorities.
+</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">1. The cost data used in the scorecard is the 2018 Capital Spend data as used in the scorecards since 2018. For the 2025 Scorecard, this data has been adjusted for inflation (rebased to 1st Quarter 2026 prices). National averages adjusted for 2023 regional location factors are shown. You can use this data to establish developer contributions per school place, by adjusting for further inflation if needed (see examples below).
 &lt;br&gt;2. Projects which do not create additional mainstream places or where the project's additional place funding is zero are removed.
@@ -1465,7 +1498,7 @@
 &lt;br&gt;6. The average cost includes costs associated with maintenance and building condition or enhancement works.
 &lt;br&gt;7. The measure does not include places in special schools or units attached to mainstream schools, or new places which were funded through central programmes (including free schools). For projects within the 2018 Capital Spend dataset, a project which creates additional mainstream places and also creates SEN places or re-provides places, has been adjusted to apportion out those costs. For projects within the Capital Spend Survey, apportioning costs is not possible and therefore a project which creates additional mainstream places and also creates SEN places or re-provides places has been excluded.
 &lt;br&gt;8. All costs have been normalised to a common UK average price level using regional location factors published by BCIS, March 2023, 1 is the base weight.
-&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2026.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2026 prices using this index (Q1 2026 index value = 399).
+&lt;br&gt;9. All costs have been adjusted for inflation using the latest BCIS All-In Tender Price of Index (TPI), published March 2026.  Costs have been rebased from the start of construction (or time of place provision if construction start date unavailable) to 1st Quarter (Jan – Mar) 2026 prices using this index (Q1 2026 index value = 410).
 10. </t>
     </r>
     <r>
@@ -1485,42 +1518,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/399).  If not, you can apply a known change to the published cost (e.g. up or down x%).
+      <t>.  If you have access to the BCIS indices via a subscription to BCIS Online (https://www.rics.org/uk/products/data-products/bcis-construction/bcis-online/) you can use the latest inflation index to re-base (weight to apply = latest index/410).  If not, you can apply a known change to the published cost (e.g. up or down x%).
 11. Some additional but limited benchmark information for similar capital programme schemes carried out by the DfE is available in the National School Delivery Cost Benchmarking study: https://documents.hants.gov.uk/property-services/NationalSchoolDeliveryBenchmarkingreport.pdf</t>
     </r>
-  </si>
-  <si>
-    <t>1. Each school has been matched with the Ofsted data as at  31 August 2025 (published November 2025). Graded judgements on four areas 'Quality of Education', 'Behaviour and Attitudes', 'Personal Development' and 'Leadership and Management' are used and where the inspection took place before 1 September 2023 the rating for 'Overall effectiveness: how good is the school is." is used for each judgement area.
-&lt;br&gt;2. There are four Ofsted categories: 'Outstanding', 'Good', 'Requires improvement' and 'Inadequate'.
-&lt;br&gt;3. The calculation counts the number of existing and new places that have been created in schools of each category. &lt;br&gt;4. Note that many schools will have been inspected some time before August 2025, and some will have been inspected since this date. &lt;br&gt;5. There are school places with no rating, as the school has yet to be inspected so do not have an Ofsted judgement.</t>
-  </si>
-  <si>
-    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2027/28 as provided in SCAP 2025.
-&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
-&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
-&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
-  </si>
-  <si>
-    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2026/27 as provided in SCAP 2024.
-&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
-&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
-&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
-  </si>
-  <si>
-    <t>1. This is the local authority's forecast of pupil numbers for the academic year 2025/26 as provided in SCAP 2023.
-&lt;br&gt;2. These forecasts cover pupils that local authorities anticipate will attend primary schools (or primary provision in middle or all-through schools i.e. years R-6) and secondary schools (or secondary provision in middle or all-through schools i.e. years 7-11)
-&lt;br&gt;3. These forecasts focus on local authorities expectations about new school places and do not include pupils who are expected to attend independent schools or special/non-mainstream provision.
-&lt;br&gt;4. Anticipated change in pupil numbers should be viewed in conjunction with an LAs forecast accuracy. Low one-year out forecast accuracy may result in the anticipated change in pupil numbers not being representative of the trend of an LAs pupil number forecasts.</t>
-  </si>
-  <si>
-    <t>Total basic need funding 2011 to 2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total amount of basic need capital funding allocated to each local authority to support them to create new mainstream primary and secondary places from 2011 to 2028. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. This refers to the amount of basic need capital funding that the Department for Education (DfE) has allocated to each local authority to create new places from the 2011-12 financial year to the 2027-28 financial year. Basic Need funding for the 2027-28 financial year is intended to support the creation of mainstream places for pupils aged 5 to 16 for the 2028/29 academic year. &lt;br&gt;2. The figure includes formula-based funding allocations and funding provided through the Targeted Basic Need Programme. Basic Need formula-based funding allocations cover the whole period and are not ring-fenced (although they can only be used for capital purposes).  Targeted Basic Need funding was provided between 2013 and 2015 and had to be spent by agreed deadlines and on specific projects. Both types of allocations are published here. &lt;br&gt;3. The figure only includes funding allocated to local authorities and does not include centrally-funded capital programmes such as the free schools programme. &lt;br&gt;4. The England total will not match the sum of allocations for all local authorities in the scorecard because the England total includes allocations to predecessor local authorities.
-</t>
   </si>
 </sst>
 </file>
@@ -2031,15 +2031,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2058,16 +2064,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2386,16 +2386,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8372DA64-5E2C-41C1-8CF4-85BC1C2AFF86}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
-    <col min="3" max="3" width="54.26953125" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-    <col min="5" max="5" width="87.26953125" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="87.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2415,11 +2415,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="52" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -2428,32 +2428,32 @@
       <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="54" t="s">
         <v>34</v>
       </c>
       <c r="F2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="54"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="54"/>
+      <c r="E3" s="53"/>
       <c r="F3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="55" t="s">
         <v>94</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -2469,9 +2469,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="53"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
@@ -2485,9 +2485,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="53"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="11" t="s">
         <v>42</v>
       </c>
@@ -2501,9 +2501,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="53"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="11" t="s">
         <v>43</v>
       </c>
@@ -2517,9 +2517,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="54"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="11" t="s">
         <v>229</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>46</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>47</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>54</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="19"/>
       <c r="C13" s="9" t="s">
@@ -2623,7 +2623,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="24"/>
       <c r="C14" s="28" t="s">
@@ -2633,17 +2633,17 @@
         <v>59</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="52" t="s">
         <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -2652,32 +2652,32 @@
       <c r="D15" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="54" t="s">
         <v>105</v>
       </c>
       <c r="F15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="54"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="4" t="s">
         <v>232</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="54"/>
+      <c r="E16" s="53"/>
       <c r="F16" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="55" t="s">
         <v>132</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -2693,9 +2693,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
-      <c r="B18" s="53"/>
+      <c r="B18" s="56"/>
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
@@ -2709,9 +2709,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
-      <c r="B19" s="53"/>
+      <c r="B19" s="56"/>
       <c r="C19" s="11" t="s">
         <v>111</v>
       </c>
@@ -2725,9 +2725,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="53"/>
+      <c r="B20" s="56"/>
       <c r="C20" s="11" t="s">
         <v>113</v>
       </c>
@@ -2741,9 +2741,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
-      <c r="B21" s="54"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>133</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>134</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>136</v>
       </c>
@@ -2811,11 +2811,11 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="55" t="s">
+    <row r="25" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="60" t="s">
         <v>139</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -2831,9 +2831,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="56"/>
-      <c r="B26" s="59"/>
+    <row r="26" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="58"/>
+      <c r="B26" s="61"/>
       <c r="C26" s="9" t="s">
         <v>119</v>
       </c>
@@ -2847,9 +2847,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="56"/>
-      <c r="B27" s="59"/>
+    <row r="27" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="58"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="9" t="s">
         <v>122</v>
       </c>
@@ -2863,9 +2863,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A28" s="56"/>
-      <c r="B28" s="59"/>
+    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="58"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="9" t="s">
         <v>125</v>
       </c>
@@ -2879,9 +2879,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="57"/>
-      <c r="B29" s="60"/>
+    <row r="29" spans="1:6" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="59"/>
+      <c r="B29" s="62"/>
       <c r="C29" s="28" t="s">
         <v>128</v>
       </c>
@@ -2889,17 +2889,17 @@
         <v>129</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F29" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="52" t="s">
         <v>176</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -2908,32 +2908,32 @@
       <c r="D30" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="62" t="s">
+      <c r="E30" s="54" t="s">
         <v>178</v>
       </c>
       <c r="F30" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="139.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="54"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="E31" s="54"/>
+      <c r="E31" s="53"/>
       <c r="F31" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="55" t="s">
         <v>179</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -2949,9 +2949,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
-      <c r="B33" s="53"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="4" t="s">
         <v>24</v>
       </c>
@@ -2965,9 +2965,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
-      <c r="B34" s="53"/>
+      <c r="B34" s="56"/>
       <c r="C34" s="11" t="s">
         <v>228</v>
       </c>
@@ -2981,9 +2981,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
-      <c r="B35" s="53"/>
+      <c r="B35" s="56"/>
       <c r="C35" s="11" t="s">
         <v>181</v>
       </c>
@@ -2997,9 +2997,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
-      <c r="B36" s="54"/>
+      <c r="B36" s="53"/>
       <c r="C36" s="11" t="s">
         <v>115</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>187</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A38" s="30" t="s">
         <v>188</v>
       </c>
@@ -3049,29 +3049,29 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:6" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>243</v>
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="51" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F39" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="55" t="s">
+    <row r="40" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="60" t="s">
         <v>192</v>
       </c>
       <c r="C40" s="9" t="s">
@@ -3087,9 +3087,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="56"/>
-      <c r="B41" s="59"/>
+    <row r="41" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="58"/>
+      <c r="B41" s="61"/>
       <c r="C41" s="9" t="s">
         <v>119</v>
       </c>
@@ -3103,9 +3103,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="56"/>
-      <c r="B42" s="59"/>
+    <row r="42" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="58"/>
+      <c r="B42" s="61"/>
       <c r="C42" s="9" t="s">
         <v>122</v>
       </c>
@@ -3119,9 +3119,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
-      <c r="B43" s="59"/>
+    <row r="43" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="58"/>
+      <c r="B43" s="61"/>
       <c r="C43" s="9" t="s">
         <v>193</v>
       </c>
@@ -3135,9 +3135,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="57"/>
-      <c r="B44" s="60"/>
+    <row r="44" spans="1:6" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="59"/>
+      <c r="B44" s="62"/>
       <c r="C44" s="28" t="s">
         <v>194</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>195</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F44" t="s">
         <v>175</v>
@@ -3153,11 +3153,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="B40:B44"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="B25:B29"/>
@@ -3166,6 +3161,11 @@
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:B44"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
@@ -3213,12 +3213,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C67D23D-5B13-4F00-9F83-043839CEFFD1}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="55.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="55.453125" style="32"/>
+    <col min="1" max="16384" width="55.42578125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -3238,11 +3238,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="55" t="s">
         <v>61</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -3251,30 +3251,30 @@
       <c r="D2" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="55" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="30"/>
-      <c r="B3" s="64"/>
+      <c r="B3" s="63"/>
       <c r="C3" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D3" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="64"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="55" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -3283,32 +3283,32 @@
       <c r="D4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="55" t="s">
         <v>70</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37"/>
-      <c r="B5" s="63"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="13" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="63"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="55" t="s">
         <v>142</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -3317,30 +3317,30 @@
       <c r="D6" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="55" t="s">
         <v>145</v>
       </c>
       <c r="F6" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="30"/>
-      <c r="B7" s="64"/>
+      <c r="B7" s="63"/>
       <c r="C7" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="64"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="30"/>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="55" t="s">
         <v>148</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -3349,32 +3349,32 @@
       <c r="D8" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="55" t="s">
         <v>151</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37"/>
-      <c r="B9" s="63"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D9" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="63"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="55" t="s">
         <v>227</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -3383,30 +3383,30 @@
       <c r="D10" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="55" t="s">
         <v>205</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
-      <c r="B11" s="64"/>
+      <c r="B11" s="63"/>
       <c r="C11" s="11" t="s">
         <v>202</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="64"/>
+      <c r="E11" s="63"/>
       <c r="F11" s="32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="30"/>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="55" t="s">
         <v>200</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -3415,41 +3415,41 @@
       <c r="D12" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="55" t="s">
         <v>206</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37"/>
-      <c r="B13" s="63"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="13" t="s">
         <v>204</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="E13" s="63"/>
+      <c r="E13" s="64"/>
       <c r="F13" s="32" t="s">
         <v>175</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
@@ -3478,9 +3478,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3163888B-9214-4218-82C5-5CD72F2D39D0}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="48.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="48.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>71</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>71</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>153</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>153</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>209</v>
       </c>
@@ -3628,14 +3628,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172A91E8-EE08-4774-802F-E9F4C78EAB63}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="37.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="37.26953125" style="32"/>
-    <col min="5" max="5" width="77.26953125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="37.26953125" style="32"/>
+    <col min="1" max="4" width="37.28515625" style="32"/>
+    <col min="5" max="5" width="77.28515625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="37.28515625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>74</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="39"/>
       <c r="B3" s="40"/>
       <c r="C3" s="11" t="s">
@@ -3689,7 +3689,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="39"/>
       <c r="B4" s="41" t="s">
         <v>100</v>
@@ -3707,7 +3707,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>96</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="203" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="255" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>85</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="240" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>86</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>98</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>99</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>89</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>90</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>156</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="11" t="s">
@@ -3879,7 +3879,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A15" s="39"/>
       <c r="B15" s="41" t="s">
         <v>162</v>
@@ -3897,7 +3897,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>18</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="261" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="315" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>165</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="240" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>168</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>98</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>99</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>212</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="39"/>
       <c r="B22" s="40"/>
       <c r="C22" s="11" t="s">
@@ -4025,7 +4025,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="195" x14ac:dyDescent="0.25">
       <c r="A23" s="39"/>
       <c r="B23" s="41" t="s">
         <v>217</v>
@@ -4037,13 +4037,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F23" s="32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="261" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="315" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>219</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="300" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>221</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>98</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>99</v>
       </c>
@@ -4167,12 +4167,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB73E146-A141-4797-B302-F0B3455C0C2E}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="57.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="57.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="57.54296875" style="32"/>
+    <col min="1" max="16384" width="57.5703125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>22</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>22</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>22</v>
       </c>
@@ -4246,45 +4246,45 @@
         <v>23</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="16"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
     </row>
@@ -4299,6 +4299,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="ec07c698-60f5-424f-b9af-f4c59398b511" ContentTypeId="0x010100545E941595ED5448BA61900FDDAFF313" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Official Document" ma:contentTypeID="0x010100545E941595ED5448BA61900FDDAFF31300C0D9F77D091A79449828113EF8250EF5" ma:contentTypeVersion="9" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="3acf8af8f3f036fb6d934619e757bc96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8c566321-f672-4e06-a901-b5e72b4c4357" xmlns:ns3="2a6436df-3f7a-48ac-8ea6-44b411e24bbc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="926947be84ee9a0228ce6a037c6848ba" ns2:_="" ns3:_="">
     <xsd:import namespace="8c566321-f672-4e06-a901-b5e72b4c4357"/>
@@ -4504,12 +4509,61 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="ec07c698-60f5-424f-b9af-f4c59398b511" ContentTypeId="0x010100545E941595ED5448BA61900FDDAFF313" PreviousValue="false"/>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Value>5</Value>
+      <Value>25</Value>
+      <Value>1</Value>
+      <Value>4</Value>
+    </TaxCatchAll>
+    <p6919dbb65844893b164c5f63a6f0eeb xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a484111e-5b24-4ad9-9778-c536c8c88985</TermId>
+        </TermInfo>
+      </Terms>
+    </p6919dbb65844893b164c5f63a6f0eeb>
+    <c02f73938b5741d4934b358b31a1b80f xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0884c477-2e62-47ea-b19c-5af6e91124c5</TermId>
+        </TermInfo>
+      </Terms>
+    </c02f73938b5741d4934b358b31a1b80f>
+    <f6ec388a6d534bab86a259abd1bfa088 xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">cc08a6d4-dfde-4d0f-bd85-069ebcef80d5</TermId>
+        </TermInfo>
+      </Terms>
+    </f6ec388a6d534bab86a259abd1bfa088>
+    <i98b064926ea4fbe8f5b88c394ff652b xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </i98b064926ea4fbe8f5b88c394ff652b>
+    <_dlc_DocIdUrl xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">
+      <Url>https://educationgovuk.sharepoint.com/sites/efappp/_layouts/15/DocIdRedir.aspx?ID=FKMV6N5X2MYP-1953928680-76369</Url>
+      <Description>FKMV6N5X2MYP-1953928680-76369</Description>
+    </_dlc_DocIdUrl>
+    <_dlc_DocId xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">FKMV6N5X2MYP-1953928680-76369</_dlc_DocId>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -4559,61 +4613,15 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00F0DC4-2D9F-43FC-8616-EC131ED26B7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Value>5</Value>
-      <Value>25</Value>
-      <Value>1</Value>
-      <Value>4</Value>
-    </TaxCatchAll>
-    <p6919dbb65844893b164c5f63a6f0eeb xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a484111e-5b24-4ad9-9778-c536c8c88985</TermId>
-        </TermInfo>
-      </Terms>
-    </p6919dbb65844893b164c5f63a6f0eeb>
-    <c02f73938b5741d4934b358b31a1b80f xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0884c477-2e62-47ea-b19c-5af6e91124c5</TermId>
-        </TermInfo>
-      </Terms>
-    </c02f73938b5741d4934b358b31a1b80f>
-    <f6ec388a6d534bab86a259abd1bfa088 xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">DfE</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">cc08a6d4-dfde-4d0f-bd85-069ebcef80d5</TermId>
-        </TermInfo>
-      </Terms>
-    </f6ec388a6d534bab86a259abd1bfa088>
-    <i98b064926ea4fbe8f5b88c394ff652b xmlns="8c566321-f672-4e06-a901-b5e72b4c4357">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </i98b064926ea4fbe8f5b88c394ff652b>
-    <_dlc_DocIdUrl xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">
-      <Url>https://educationgovuk.sharepoint.com/sites/efappp/_layouts/15/DocIdRedir.aspx?ID=FKMV6N5X2MYP-1953928680-76369</Url>
-      <Description>FKMV6N5X2MYP-1953928680-76369</Description>
-    </_dlc_DocIdUrl>
-    <_dlc_DocId xmlns="2a6436df-3f7a-48ac-8ea6-44b411e24bbc">FKMV6N5X2MYP-1953928680-76369</_dlc_DocId>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E94FF3-D2F7-4169-BE5C-5ED202BAA024}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4632,31 +4640,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00F0DC4-2D9F-43FC-8616-EC131ED26B7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C56A4F-6917-41AA-BBE5-DA7C75896563}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035EEA42-582A-4724-B162-C22729062C2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{334E8BC2-6B82-4EDA-BE50-EFE4767E8CD2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="8c566321-f672-4e06-a901-b5e72b4c4357"/>
@@ -4673,6 +4657,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035EEA42-582A-4724-B162-C22729062C2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9C56A4F-6917-41AA-BBE5-DA7C75896563}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{de278828-447b-4aaa-a336-d38da9839a3c}" enabled="1" method="Privileged" siteId="{fad277c9-c60a-4da1-b5f3-b3b8b34a82f9}" contentBits="3" removed="0"/>
